--- a/public/assets/template/Template_Tarif.xlsx
+++ b/public/assets/template/Template_Tarif.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raynandapamungkas/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5436AB81-309D-C54A-BCE5-D54C38938318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C681FAFF-E78D-4D28-B273-A94949EED868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{394BB966-B45D-4333-9558-4476935831FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{394BB966-B45D-4333-9558-4476935831FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="6">
   <si>
     <t>Asal Gerbang</t>
   </si>
@@ -44,37 +45,7 @@
     <t>Denda</t>
   </si>
   <si>
-    <t>investor 8</t>
-  </si>
-  <si>
-    <t>investor 9</t>
-  </si>
-  <si>
-    <t>investor 10</t>
-  </si>
-  <si>
     <t>normal</t>
-  </si>
-  <si>
-    <t>MTN</t>
-  </si>
-  <si>
-    <t>JM-JANGER</t>
-  </si>
-  <si>
-    <t>MMS</t>
-  </si>
-  <si>
-    <t>BSD</t>
-  </si>
-  <si>
-    <t>JKC</t>
-  </si>
-  <si>
-    <t>CSJ</t>
-  </si>
-  <si>
-    <t>TLKJ</t>
   </si>
   <si>
     <t>Benda Utama 3</t>
@@ -82,12 +53,15 @@
   <si>
     <t>Total</t>
   </si>
+  <si>
+    <t>00000</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,6 +73,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -202,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -211,6 +191,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -556,21 +545,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA8F9DC-FA4C-4B1F-9547-B630C1D6E852}">
   <dimension ref="A1:BP4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="22" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="3.83203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="37" width="1.83203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="52" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="53" max="57" width="3.83203125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="57" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -578,84 +561,84 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="7"/>
       <c r="H1" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="7"/>
       <c r="M1" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S1" s="6"/>
       <c r="T1" s="6"/>
       <c r="U1" s="6"/>
       <c r="V1" s="7"/>
       <c r="W1" s="5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
       <c r="AA1" s="7"/>
       <c r="AB1" s="5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AC1" s="6"/>
       <c r="AD1" s="6"/>
       <c r="AE1" s="6"/>
       <c r="AF1" s="7"/>
       <c r="AG1" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AH1" s="6"/>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="6"/>
       <c r="AK1" s="7"/>
       <c r="AL1" s="5" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM1" s="6"/>
       <c r="AN1" s="6"/>
       <c r="AO1" s="6"/>
       <c r="AP1" s="7"/>
       <c r="AQ1" s="5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AR1" s="6"/>
       <c r="AS1" s="6"/>
       <c r="AT1" s="6"/>
       <c r="AU1" s="7"/>
       <c r="AV1" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW1" s="6"/>
       <c r="AX1" s="6"/>
       <c r="AY1" s="6"/>
       <c r="AZ1" s="7"/>
-      <c r="BA1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="BB1" s="6"/>
-      <c r="BC1" s="6"/>
-      <c r="BD1" s="6"/>
-      <c r="BE1" s="7"/>
+      <c r="BA1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BB1" s="9"/>
+      <c r="BC1" s="9"/>
+      <c r="BD1" s="9"/>
+      <c r="BE1" s="10"/>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="1">
@@ -824,12 +807,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
         <v>0</v>
@@ -847,34 +830,34 @@
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O3" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P3" s="1">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="1">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R3" s="1">
         <v>0</v>
@@ -892,19 +875,19 @@
         <v>0</v>
       </c>
       <c r="W3" s="1">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="X3" s="1">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="1">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="1">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="1">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
@@ -982,28 +965,28 @@
         <v>0</v>
       </c>
       <c r="BA3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP3" s="2"/>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1021,34 +1004,34 @@
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="M4" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N4" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O4" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P4" s="1">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="1">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R4" s="1">
         <v>0</v>
@@ -1066,19 +1049,19 @@
         <v>0</v>
       </c>
       <c r="W4" s="1">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="X4" s="1">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="1">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="1">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="1">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="1">
         <v>0</v>
@@ -1156,19 +1139,19 @@
         <v>0</v>
       </c>
       <c r="BA4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP4" s="2"/>
     </row>
@@ -1188,6 +1171,7 @@
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="W1:AA1"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B4" xr:uid="{9A8ABE7A-4490-4F51-86AF-FD5DACACDCA1}">
       <formula1>"normal, ags, khl"</formula1>
@@ -1195,4 +1179,13 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{038F7983-6E5C-4650-A20C-84FCFB2E622D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>